--- a/construction-estimates/ops/estimate-template.xlsx
+++ b/construction-estimates/ops/estimate-template.xlsx
@@ -494,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TAKEOFF DESK: ESTIMATE</t>
+          <t>PALMETTO TAKEOFFS: ESTIMATE</t>
         </is>
       </c>
     </row>
